--- a/Auftrag_test1.xlsx
+++ b/Auftrag_test1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/37285d1b3bdcff71/Desktop/AG/LegoLAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F76F995-E815-4398-8A2F-B2F5887D6818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{0F76F995-E815-4398-8A2F-B2F5887D6818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9511AB2-6654-4163-A609-289572C7AC75}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{608330B3-2821-42BF-90AB-F28B60B6AA0F}"/>
   </bookViews>
@@ -419,10 +419,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E75218D-6385-4353-B4BC-CC68C7EA9A03}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>362201</v>
       </c>
@@ -432,8 +432,20 @@
       <c r="D1">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>4160228</v>
       </c>
@@ -444,7 +456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>6034044</v>
       </c>
@@ -455,7 +467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>302301</v>
       </c>
@@ -466,7 +478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>243101</v>
       </c>
@@ -477,7 +489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4206482</v>
       </c>
@@ -488,7 +500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>306924</v>
       </c>
@@ -499,7 +511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>614124</v>
       </c>
@@ -508,20 +520,6 @@
       </c>
       <c r="D8">
         <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
